--- a/www/download/COUNTRY.EST.zdW16.xlsx
+++ b/www/download/COUNTRY.EST.zdW16.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>Estônia</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,1848 +852,3409 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1.08191322132095</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1.12189530328975</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1.05970074165817</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.88402476623831</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.804332991294144</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.80326231801864</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.795529958239355</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0.729975790600401</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>0.680188315181349</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0.717520719435623</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0.75310469592496</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>0.718225658468364</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>0.777893501365584</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>0.752956577652614</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.752711379649273</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0.589</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0.592</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>0.589</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0.606</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>0.604</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>0.618</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0.647</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>0.649</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0.646</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0.583</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>0.552</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>0.59</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>0.589</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>0.607</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>0.619</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.538</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.544</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>0.543</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0.552</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>0.545</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>0.569</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0.593</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0.588</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>0.594</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>0.532</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>0.504</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0.538</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>0.535</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>0.549</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>0.561</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>1145.697</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1154.004</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>1147.224</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>1188.425</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>1187.862</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>1236.342</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>1287.935</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>1290.606</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>1267.15</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>1064.285</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>1031.077</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>1127.48</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1105.17</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>1127.236</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>1148.028</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1042.838</t>
+          <t>1187477960.33929</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1057.137</t>
+          <t>1175237689.28588</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1054.244</t>
+          <t>1271757760.68488</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1079.232</t>
+          <t>1357241522.10637</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1070.003</t>
+          <t>1345590413.79625</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1134.384</t>
+          <t>1350824162.22343</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1178.243</t>
+          <t>1506278678.46318</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>1167.145</t>
+          <t>1474548156.35829</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>1162.127</t>
+          <t>1442993819.20048</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>972.034</t>
+          <t>1106464169.30229</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>941.215</t>
+          <t>1096803867.36696</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1025.968</t>
+          <t>1329624310.61134</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1002.652</t>
+          <t>1272265504.82813</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>1019.821</t>
+          <t>1232817254.56375</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>1040.607</t>
+          <t>1291812427.38635</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>277805244.420741</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>267402502.581567</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>328878477.714478</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>379093069.271395</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>359364930.104823</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>366483716.593505</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>443847939.114903</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>460386601.477422</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>470599277.327412</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>339557330.72382</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>299099132.03321</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>331346952.372528</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>318730157.016399</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>327125488.404421</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>386549032.59782</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>5133260.07299615</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>4770016.01661283</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>4107671.20813364</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>3406367.72858758</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2840549.23639929</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2364497.95801577</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2183477.79706426</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>1681987.58582108</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>1522820.68464039</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1567100.72323868</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>1421427.54006329</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>1363837.83903596</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1354650.68982943</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>1226322.28243188</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>1202599.39172729</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>5926.42531597586</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5920.57913017528</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>6010.26831942064</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>6932.9955499071</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>7659.04203571804</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>8321.04128653574</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>9142.59028817874</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>10383.6913407542</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>10812.4762464529</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>8167.66306440749</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>8518.14582765431</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>10321.0190514754</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>9716.1536300415</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>9395.50645245352</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>9609.60761755279</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>10772.0160704543</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10504.8746419326</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>11451.2373772179</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>13304.9594207036</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>14536.4689750434</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>15761.6665464105</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>18572.2799951684</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>20394.9175270408</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>21767.9545208192</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>15254.1178847484</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>16706.0147998885</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>21593.3910002515</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>20182.8260225721</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>19443.6326971038</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>20445.2139607153</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2.75384562006541</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2.95335492298744</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2.2055730959545</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>1.84687874160889</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>1.97748308297053</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2.09531896954165</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>1.65460959974172</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>1.53514111022025</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>1.46946193075317</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1.86265061021642</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>2.14683293663151</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>2.09635562558765</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>2.14577073404577</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>2.11752228471787</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>1.69204398988287</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.08191322132095</t>
+          <t>516.270664227357</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.12189530328975</t>
+          <t>491.63909281406</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.05970074165817</t>
+          <t>605.446387545062</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.88402476623831</t>
+          <t>686.514069669313</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.804332991294144</t>
+          <t>659.506203165394</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.80326231801864</t>
+          <t>644.650337015839</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.795529958239355</t>
+          <t>748.352620325245</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.729975790600401</t>
+          <t>783.503406190302</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.680188315181349</t>
+          <t>792.922118496061</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.717520719435623</t>
+          <t>637.666348777126</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>0.75310469592496</t>
+          <t>592.862501552448</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>0.718225658468364</t>
+          <t>616.115567818014</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>0.777893501365584</t>
+          <t>595.645967139598</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>0.752956577652614</t>
+          <t>596.29144805764</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0.752711379649273</t>
+          <t>688.912907855676</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>23645388.5242893</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>25312365.812139</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>84867404.0271526</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>125502890.974521</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>89174390.7141904</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>89228173.7252925</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>168278210.617948</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>198200207.735379</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>248934950.659785</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>168701562.815336</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>178235232.376949</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>246194765.080775</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>230140567.571636</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>255875772.911655</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>337407210.404598</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>30888106.9598303</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>31728824.5804707</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>106386790.020777</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>120986696.158449</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>55645494.9194581</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>44236406.8521482</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>122878274.422218</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>130156277.12733</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>168194071.825917</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>84037680.1459678</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>130124654.016237</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>176983314.204981</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>152021132.196873</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>163259302.39253</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>235115772.099947</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>-7242718.43554098</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>-6416458.76833167</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>-21519385.9936246</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>4516194.81607258</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>33528895.7947323</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>44991766.8731443</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>45399936.1957305</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>68043930.608049</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>80740878.8338683</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>84663882.6693684</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>48110578.3607122</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>69211450.8757939</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>78119435.3747631</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>92616470.5191247</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>102291438.304651</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>1938.00037167813</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>1943.62382790954</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>1940.80265095729</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>1954.42231075697</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>1963.66856303909</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>1995.39841688654</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>1986.58404990727</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>1986.29169503063</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>1958.09098567818</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>1825.41596244131</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>1865.63924677899</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>1907.71290442544</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>1873.76565128013</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>1858.95187750638</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>1854.58385314561</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>1943.83651394166</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>1948.67283963</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>1947.08715258539</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>1960.127556248</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>1967.31104433861</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>2001.2005413247</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>1991.24173841846</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>1989.22045735788</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>1960.31830962273</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>1826.15750739646</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>1868.56944420092</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>1909.68892423429</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>1875.39450998647</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>1858.28551216749</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>1854.05041423765</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2035.10866808925</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2332.5662798231</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>2754.24020521407</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>4035.33595364029</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>5707.44626082175</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>7214.26650484751</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>8559.33834814697</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>11568.7386149291</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>13514.7312674653</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>9503.31208083091</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>11900.5155294324</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>16300.4598949729</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>16141.7273481383</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>17740.870446419</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>18266.2026751551</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>273953947.951764</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>297271864.6938</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>339408777.306963</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>386786784.010261</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>413192195.724656</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>450601717.648975</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>477029365.237851</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>498502724.471114</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>537659383.504582</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>380612498.640945</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>439381694.576354</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>581840182.242478</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>559960450.14446</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>560697351.091875</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>565587835.652653</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>3240.64118368168</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>3575.70843898272</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>4207.48578622364</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>5651.26925160708</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>7349.69013333132</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>8635.09182749486</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>10938.1606403447</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>13932.8830209146</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>14666.6727247837</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>9423.58179092973</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>11460.7681000581</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>15712.2957127767</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>16499.8356369344</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>17785.0972147427</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>18105.3350902218</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1145.697</t>
+          <t>462461802.758721</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1154.004</t>
+          <t>499521741.507706</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1147.224</t>
+          <t>632422420.515846</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1188.425</t>
+          <t>730456452.710201</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1187.862</t>
+          <t>704401730.533185</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>1236.342</t>
+          <t>698364399.146179</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>1287.935</t>
+          <t>886196257.338073</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>1290.606</t>
+          <t>901984991.25252</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>1267.15</t>
+          <t>873921634.453357</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>1064.285</t>
+          <t>542524890.855348</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1031.077</t>
+          <t>584236797.266673</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1127.48</t>
+          <t>785769013.606614</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1105.17</t>
+          <t>816006389.267142</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>1127.236</t>
+          <t>819804365.121224</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>1148.028</t>
+          <t>891354817.32238</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1042.838</t>
+          <t>-1205.53251559243</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1057.137</t>
+          <t>-1243.14215915962</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1054.244</t>
+          <t>-1453.24558100957</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>1079.232</t>
+          <t>-1615.93329796679</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1070.003</t>
+          <t>-1642.24387250958</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>1134.384</t>
+          <t>-1420.82532264735</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>1178.243</t>
+          <t>-2378.82229219776</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>1167.145</t>
+          <t>-2364.14440598554</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>1162.127</t>
+          <t>-1151.94145731838</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>972.034</t>
+          <t>79.7302899011836</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>941.215</t>
+          <t>439.747429374338</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1025.968</t>
+          <t>588.164182196186</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1002.652</t>
+          <t>-358.10828879616</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>1019.821</t>
+          <t>-44.2267683237279</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>1040.607</t>
+          <t>160.867584933351</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1288.663</t>
+          <t>-188507854.806957</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1289.543</t>
+          <t>-202249876.813905</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1400.325</t>
+          <t>-293013643.208883</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>1507.658</t>
+          <t>-343669668.699939</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>1482.128</t>
+          <t>-291209534.808529</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>1487.14</t>
+          <t>-247762681.497204</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>1671.939</t>
+          <t>-409166892.100222</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>1636.016</t>
+          <t>-403482266.781407</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>1613.994</t>
+          <t>-336262250.948775</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>1249.822</t>
+          <t>-161912392.214403</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1236.458</t>
+          <t>-144855102.690319</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1507.63</t>
+          <t>-203928831.364136</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1453.256</t>
+          <t>-256045939.122682</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>1423.515</t>
+          <t>-259107014.029349</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>1291.812</t>
+          <t>-325766981.669726</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>2339.808588466</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>2563.9104987282</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>2988.77422675108</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>4066.72281352046</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>4841.49807691565</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>5644.17906544559</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>6798.34652028559</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>8955.66098474175</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>9635.64000190244</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>7321.63183798102</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>7523.98613495958</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>9169.99637991748</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>8760.40762462102</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>9693.82339670197</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>10154.5573401734</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>653.313</t>
+          <t>0.161606324061936</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>662.368</t>
+          <t>0.150402225749391</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>667.492</t>
+          <t>0.161072035313462</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>707.236</t>
+          <t>0.163294916963837</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>708.971</t>
+          <t>0.155946639976705</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>713.139</t>
+          <t>0.162627464266693</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>741.497</t>
+          <t>0.160396365986806</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>750.739</t>
+          <t>0.151685896540214</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>716.757</t>
+          <t>0.13318458648262</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>592.445</t>
+          <t>0.107952621249378</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>559.244</t>
+          <t>0.12423421448921</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>635.522</t>
+          <t>0.141771059033256</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>612.478</t>
+          <t>0.139960083732336</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>595.719</t>
+          <t>0.13436516156939</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>607.174</t>
+          <t>0.132655326556566</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>2563.13702872089</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>2763.80602467209</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>3238.75030361735</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>4367.96985159235</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>5313.07922046363</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6123.64543493402</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7404.24941561593</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>10063.4532593967</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>12066.0912700792</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>9973.74685887986</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>9223.65161777288</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>10382.2632721936</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>10207.2110358754</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>11435.5003444188</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>12397.646807778</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>307.35</t>
+          <t>2666.53582850719</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>297.998</t>
+          <t>2885.51724349765</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>366.831</t>
+          <t>3371.34435374679</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>424.773</t>
+          <t>4543.08067349507</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>399.654</t>
+          <t>5536.80460510587</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>408.875</t>
+          <t>6358.19558984601</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>497.049</t>
+          <t>7693.70831560295</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>512.825</t>
+          <t>10503.35092247</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>527.872</t>
+          <t>12586.2966991226</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>386.663</t>
+          <t>10359.8935331306</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>337.653</t>
+          <t>9601.65464919127</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>375.376</t>
+          <t>10825.3631923332</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>363.117</t>
+          <t>10568.5041700282</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>374.045</t>
+          <t>11814.9357443486</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>386.549</t>
+          <t>12820.9068496977</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>239.3</t>
+          <t>14854.0688350661</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>254.75</t>
+          <t>17642.0975731334</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>187.39</t>
+          <t>19465.8564937375</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>154.07</t>
+          <t>26009.8969187024</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>167.73</t>
+          <t>32944.341824537</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>177.44</t>
+          <t>37026.1701857779</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>137.05</t>
+          <t>44789.0932095577</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>127.59</t>
+          <t>59360.1940186161</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>120.15</t>
+          <t>67380.5336649981</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>151.39</t>
+          <t>62899.3125906776</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>178.75</t>
+          <t>60123.9353766553</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>173.32</t>
+          <t>67160.8273697215</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>176.12</t>
+          <t>66676.6684373134</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>172.65</t>
+          <t>76581.2660947353</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>169.2</t>
+          <t>79706.5825745033</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>5.606</t>
+          <t>4956.3884630087</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>5.271</t>
+          <t>5160.42735073385</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>4.579</t>
+          <t>5360.79840329607</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>3.824</t>
+          <t>5740.57826829525</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>3.149</t>
+          <t>5922.94886300726</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>6294.38988420144</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2.452</t>
+          <t>6925.08230978035</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>1.891</t>
+          <t>7579.0768473652</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>1.728</t>
+          <t>7793.59008704693</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>6913.96867151096</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1.626</t>
+          <t>6687.14182353861</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1.572</t>
+          <t>6877.26372030622</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1.575</t>
+          <t>7054.78221887549</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>7573.03219009935</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>1.203</t>
+          <t>7913.35974285423</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>4785.57491076776</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>4954.77444979079</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>5182.2111995454</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>5520.21227720647</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>5700.60682286671</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>6089.88779526249</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>6686.25225592169</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>7298.94661895551</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>7482.64837695036</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>6647.56286930432</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>6423.84474822377</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>6607.80159158942</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>6824.67093327994</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>7347.67877417172</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>7660.61491742571</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>2400.511461798</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2653.41074188718</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>3135.40512456607</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>4247.28395757746</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>5137.55941378058</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>6021.47216882011</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>7184.00778665739</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>9004.10424851486</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>8974.04851315105</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>6790.14566894767</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>7469.44988351882</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>9521.46162175513</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>9332.07209747962</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>10289.8541920075</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>10573.5027401286</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>1042838000</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1057137000</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>1054244000</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>1079232000</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>1070003000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>1134384000</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>1178243000</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>1167145000</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>1162127000</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>972034000</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>941215000</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>1025968000</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>1002652000</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>1019821000</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>1040607000</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>1145697241.31722</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1154004055.62888</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>1147223750.30331</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>1188425337.35316</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>1187862408.57165</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>1236341694.4304</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>1287935156.40906</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>1290606232.73379</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>1267149755.34013</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>1064284595.31066</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>1031076619.31007</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>1127480340.86792</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>1105169984.73503</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>1127235991.6808</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>1148028016.49595</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>653313121.730361</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>662367517.305403</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>667491654.153334</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>707236236.908044</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>708970903.444176</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>713139285.849883</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>741496941.710482</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>750738653.510219</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>716757120.149308</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>592445043.101207</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>559243805.208966</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>635522129.940804</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>612477513.767772</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>595719053.655805</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>607174401.134361</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>589400</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>592200</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>589200</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>606300</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>603800</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>617800</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>646800</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>648800</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>646400</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>582800</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>551800</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>590400</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>589300</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>606600</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>619200</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>538100</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>543900</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>543200</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>552200</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>544900</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>568500</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>593100</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>587600</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>593500</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>532500</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>504500</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>537800</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>535100</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>548600</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>561100</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>1145697241.31722</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1154004055.62888</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>1147223750.30331</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>1188425337.35316</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>1187862408.57165</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>1236341694.4304</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>1287935156.40906</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>1290606232.73379</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>1267149755.34013</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>1064284595.31066</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>1031076619.31007</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>1127480340.86792</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>1105169984.73503</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>1127235991.6808</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>1148028016.49595</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>1042838000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1057137000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>1054244000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>1079232000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>1070003000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>1134384000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>1178243000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>1167145000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>1162127000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>972034000</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>941215000</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>1025968000</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>1002652000</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>1019821000</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>1040607000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>11786.2372750432</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>13060.7993377414</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>15297.9866404659</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>20138.2232260324</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>24827.3330292857</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>28656.3510239008</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>34086.51278339</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>43944.4287437199</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>48629.5355227539</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>36981.5841510545</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>38925.1354716147</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>47853.4408140883</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>47221.2050453434</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>52216.6670370017</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>54483.1692395794</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>5067.32435504318</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>5538.74449774145</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>6507.12168046594</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>8790.81666603235</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>10674.6119992857</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>12379.4174939008</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>14877.84174339</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>19507.1802937199</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>21560.3440027539</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>17149.7598310545</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>17070.8384016147</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>20346.8248140884</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>19900.4469653434</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>22104.9213570017</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>23393.7450895794</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>24334.8749314343</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>28109.5267712054</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>28132.1217093348</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>30410.8298874927</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>33334.1162302613</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>35531.9738382023</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>39134.9388720482</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>42800.2256281273</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>42513.7142157278</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>42532.4219860595</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>41871.5030491439</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>42210.5169229735</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>43605.3308417622</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>46736.8226183926</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>47654.0253789849</t>
         </is>
       </c>
     </row>
@@ -2699,7 +4265,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2722,36 +4288,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -2763,331 +4344,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3124,6 +5069,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>zdW16</t>
